--- a/public/templates/Statement_Template.xlsx
+++ b/public/templates/Statement_Template.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>Basic Salary</t>
   </si>
@@ -93,22 +93,31 @@
     <t>Gross Salary</t>
   </si>
   <si>
-    <t>STS117</t>
-  </si>
-  <si>
-    <t>Surya B</t>
-  </si>
-  <si>
-    <t>STS144</t>
-  </si>
-  <si>
-    <t>Chanchala Bangera</t>
-  </si>
-  <si>
-    <t>STS143</t>
-  </si>
-  <si>
-    <t>Rita B</t>
+    <t>Payslip_generation</t>
+  </si>
+  <si>
+    <t>Payslip Action</t>
+  </si>
+  <si>
+    <t>STS139</t>
+  </si>
+  <si>
+    <t>Chiru Bangera</t>
+  </si>
+  <si>
+    <t>disabled</t>
+  </si>
+  <si>
+    <t>STS122</t>
+  </si>
+  <si>
+    <t>Karna Bangera</t>
+  </si>
+  <si>
+    <t>STS079</t>
+  </si>
+  <si>
+    <t>Ventak Bangera</t>
   </si>
 </sst>
 </file>
@@ -453,7 +462,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -461,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF4"/>
+  <dimension ref="A1:AM4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -487,7 +496,7 @@
     <col min="21" max="21" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:39">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -557,8 +566,12 @@
       <c r="W1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
@@ -566,28 +579,35 @@
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:39">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1">
-        <v>700000</v>
+        <v>200000</v>
       </c>
       <c r="D2" s="1">
-        <v>20416.666666666668</v>
+        <v>77777</v>
       </c>
       <c r="E2" s="1">
-        <v>2041.666666666667</v>
+        <v>666.66666666666686</v>
       </c>
       <c r="F2" s="1">
-        <v>7484.166666666667</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="G2" s="1">
-        <v>7583.3333333333339</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
@@ -596,34 +616,34 @@
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>2916.6666666666665</v>
+        <v>1333.3333333333333</v>
       </c>
       <c r="K2" s="1">
-        <v>116666.66666666667</v>
+        <v>23000</v>
       </c>
       <c r="L2" s="1">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="M2" s="1">
-        <v>2450</v>
+        <v>800.00000000000011</v>
       </c>
       <c r="N2" s="1">
-        <v>2450</v>
+        <v>800.00000000000011</v>
       </c>
       <c r="O2" s="1">
-        <v>612.5</v>
+        <v>50.000000000000007</v>
       </c>
       <c r="P2" s="1">
-        <v>816.66666666666674</v>
+        <v>403.33333333333337</v>
       </c>
       <c r="Q2" s="1">
-        <v>14.083333333333334</v>
+        <v>366.66666666666674</v>
       </c>
       <c r="R2" s="1">
-        <v>2333.33</v>
+        <v>0</v>
       </c>
       <c r="S2" s="1">
-        <v>816.66666666666674</v>
+        <v>66.666666666666686</v>
       </c>
       <c r="T2" s="1">
         <v>0</v>
@@ -632,13 +652,17 @@
         <v>0</v>
       </c>
       <c r="V2" s="1">
-        <v>157109.16666666669</v>
+        <v>35000</v>
       </c>
       <c r="W2" s="1">
-        <v>148065.92000000001</v>
-      </c>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
+        <v>25813.333333333336</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>0</v>
+      </c>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
@@ -646,28 +670,35 @@
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
       <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:39">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="D3" s="1">
-        <v>14583.333333333332</v>
+        <v>77777</v>
       </c>
       <c r="E3" s="1">
-        <v>1458.3333333333333</v>
+        <v>2666.6666666666674</v>
       </c>
       <c r="F3" s="1">
-        <v>2083.3333333333335</v>
+        <v>5933.3333333333348</v>
       </c>
       <c r="G3" s="1">
-        <v>2083.3333333333335</v>
+        <v>3333.3333333333339</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
@@ -676,49 +707,53 @@
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>2916.6666666666665</v>
+        <v>2000</v>
       </c>
       <c r="K3" s="1">
-        <v>83333.333333333328</v>
+        <v>23000</v>
       </c>
       <c r="L3" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M3" s="1">
-        <v>1749.9999999999998</v>
+        <v>2933.3333333333339</v>
       </c>
       <c r="N3" s="1">
-        <v>1749.9999999999998</v>
+        <v>2933.3333333333339</v>
       </c>
       <c r="O3" s="1">
-        <v>291.66666666666663</v>
+        <v>733.33333333333348</v>
       </c>
       <c r="P3" s="1">
-        <v>874.99999999999989</v>
+        <v>1066.666666666667</v>
       </c>
       <c r="Q3" s="1">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="R3" s="1">
-        <v>2916.67</v>
+        <v>3333.33</v>
       </c>
       <c r="S3" s="1">
-        <v>437.49999999999994</v>
+        <v>533.33333333333348</v>
       </c>
       <c r="T3" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U3" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="V3" s="1">
-        <v>106458.33333333333</v>
+        <v>63600.000000000007</v>
       </c>
       <c r="W3" s="1">
-        <v>93424.996666666659</v>
-      </c>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
+        <v>47037.670000000006</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>0</v>
+      </c>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
@@ -726,79 +761,90 @@
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1"/>
+      <c r="AM3" s="1"/>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:39">
       <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1">
+        <v>40000</v>
+      </c>
+      <c r="D4" s="1">
+        <v>77777</v>
+      </c>
+      <c r="E4" s="1">
+        <v>133.33333333333334</v>
+      </c>
+      <c r="F4" s="1">
+        <v>296.66666666666669</v>
+      </c>
+      <c r="G4" s="1">
+        <v>166.66666666666669</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>100</v>
+      </c>
+      <c r="K4" s="1">
+        <v>23000</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>146.66666666666669</v>
+      </c>
+      <c r="N4" s="1">
+        <v>146.66666666666669</v>
+      </c>
+      <c r="O4" s="1">
+        <v>36.666666666666671</v>
+      </c>
+      <c r="P4" s="1">
+        <v>53.333333333333343</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>29</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1">
+        <v>26.666666666666671</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0</v>
+      </c>
+      <c r="V4" s="1">
+        <v>25030</v>
+      </c>
+      <c r="W4" s="1">
+        <v>24591</v>
+      </c>
+      <c r="X4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="1">
-        <v>900000</v>
-      </c>
-      <c r="D4" s="1">
-        <v>26250</v>
-      </c>
-      <c r="E4" s="1">
-        <v>2625</v>
-      </c>
-      <c r="F4" s="1">
-        <v>3750</v>
-      </c>
-      <c r="G4" s="1">
-        <v>3750</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1">
-        <v>5250.0000000000009</v>
-      </c>
-      <c r="K4" s="1">
-        <v>150000</v>
-      </c>
-      <c r="L4" s="1">
-        <v>11500</v>
-      </c>
-      <c r="M4" s="1">
-        <v>3150</v>
-      </c>
-      <c r="N4" s="1">
-        <v>3150</v>
-      </c>
-      <c r="O4" s="1">
-        <v>525</v>
-      </c>
-      <c r="P4" s="1">
-        <v>1575</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="R4" s="1">
-        <v>5250</v>
-      </c>
-      <c r="S4" s="1">
-        <v>787.5</v>
-      </c>
-      <c r="T4" s="1">
-        <v>3</v>
-      </c>
-      <c r="U4" s="1">
-        <v>9000</v>
-      </c>
-      <c r="V4" s="1">
-        <v>191625</v>
-      </c>
-      <c r="W4" s="1">
-        <v>156675</v>
-      </c>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
+      <c r="Y4" s="1">
+        <v>0</v>
+      </c>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
@@ -806,6 +852,13 @@
       <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="1"/>
+      <c r="AI4" s="1"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="1"/>
+      <c r="AL4" s="1"/>
+      <c r="AM4" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F1:O1 T1">
